--- a/assets/docs/lop2/Tu nhien va Xa hoi - Lop 2.xlsx
+++ b/assets/docs/lop2/Tu nhien va Xa hoi - Lop 2.xlsx
@@ -1112,7 +1112,7 @@
       <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Tích hợp AI - YCCĐ 2.D1.1: HS đề xuất ý tưởng dùng máy thông minh để nhắc nhở các bạn bỏ rác đúng nơi quy định; hiểu AI chỉ hỗ trợ nhắc nhở, còn con người vẫn phải tự giác hành động đúng.
-QPAN: Giới thiệu tinh thần đoàn kết toàn dân tộc và sự hi sinh của các chiến sĩ cách mạng; kể việc làm của các chú bộ đội, công an giúp dân ở địa phương.</t>
+Học tập và làm theo Bác: Điều 4 “Giữ gìn vệ sinh thật tốt” (mạch 4): HS nhận một việc giữ vệ sinh lớp, trường (nhặt rác ở góc lớp, xếp gọn dép, tưới cây) và làm ngay sau tiết học.</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <is>
           <t>Tích hợp AI - YCCĐ 2.A1.2: HS nhận biết các phương tiện giao thông thông minh (AI) vẫn cần con người giám sát an toàn.
 Năng lực số 1.1 CB1b: HS gọi tên được các phương tiện giao thông và loại đường tương ứng.
-STEM: Các loại đường và phương tiện giao thông (TNXH – Mĩ thuật) — dạy thay cho tiết này.
+STEM: Sa bàn giao thông an toàn (TNXH – Toán – Công nghệ – Mĩ thuật) — dạy thay cho tiết này.
 QPAN: Liên hệ công việc giữ gìn an ninh, trật tự, cứu hộ – cứu nạn của bộ đội, công an; nhắc HS chấp hành quy định an toàn.</t>
         </is>
       </c>
@@ -1406,7 +1406,8 @@
       <c r="H30" s="4" t="inlineStr">
         <is>
           <t>Tích hợp AI - YCCĐ 2.A1.2: HS nhận biết AI/camera có thể hỗ trợ nhận diện biển báo nhưng con người vẫn phải quan sát, kiểm tra và chịu trách nhiệm về an toàn.
-Năng lực số 1.1 CB1b: HS gọi tên được các phương tiện giao thông và loại đường tương ứng.</t>
+Năng lực số 1.1 CB1b: HS gọi tên được các phương tiện giao thông và loại đường tương ứng.
+STEM: Sa bàn giao thông an toàn (TNXH – Toán – Công nghệ – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
